--- a/src/test/resources/testData.xlsx
+++ b/src/test/resources/testData.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91798\eclipse-workspace\selinium\Selinium\AdvanceSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299A7EEB-E387-4900-A37F-E733E5FACAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5174416-D7BE-488D-B4B8-17447F9AFC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{3A6B9A5C-B1B1-4EB0-85EF-F7DA12AEC90D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{3A6B9A5C-B1B1-4EB0-85EF-F7DA12AEC90D}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
     <sheet name="Leads" sheetId="2" r:id="rId2"/>
+    <sheet name="OpportunitiesPage" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>TC_ID</t>
   </si>
@@ -86,6 +87,25 @@
   </si>
   <si>
     <t>ganiCompeny</t>
+  </si>
+  <si>
+    <t>TestCasr ID</t>
+  </si>
+  <si>
+    <t>TestCase Name</t>
+  </si>
+  <si>
+    <t>Opportunitie Name</t>
+  </si>
+  <si>
+    <t>T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Orinization with 
+valid credentials </t>
+  </si>
+  <si>
+    <t>Ramakirshna Mission</t>
   </si>
 </sst>
 </file>
@@ -172,13 +192,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,4 +636,42 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB29105-13E4-481C-9314-18F7D70AE334}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" style="6" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>